--- a/Result/profitability/6269.xlsx
+++ b/Result/profitability/6269.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.06</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.54375</v>
+        <v>-1.625</v>
       </c>
       <c r="N2" t="n">
-        <v>3.49875</v>
+        <v>3.3825</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.61</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.33875</v>
+        <v>-1.32</v>
       </c>
       <c r="N3" t="n">
-        <v>4.845</v>
+        <v>5.4525</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.87</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.00125</v>
+        <v>-0.9912499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>8.584999999999999</v>
+        <v>9.053749999999999</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.51</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.7175</v>
+        <v>-0.75125</v>
       </c>
       <c r="N5" t="n">
-        <v>11.42125</v>
+        <v>11.6625</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.26</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.50875</v>
+        <v>-0.47875</v>
       </c>
       <c r="N6" t="n">
-        <v>13.30375</v>
+        <v>13.67</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.77</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1725</v>
+        <v>-0.15</v>
       </c>
       <c r="N7" t="n">
-        <v>16.27375</v>
+        <v>16.68125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.02</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1875</v>
+        <v>0.3025</v>
       </c>
       <c r="N8" t="n">
-        <v>19.71375</v>
+        <v>20.42125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>0.74</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8887499999999999</v>
+        <v>0.8887500000000002</v>
       </c>
       <c r="N13" t="n">
         <v>23.47375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6269</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5380</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5150</v>
+      </c>
+      <c r="E75" t="n">
+        <v>230</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-701</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-13.02%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>62</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-638</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-535</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-1.76125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>1.5975</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.9200000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.3538461538461539</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>5.66</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-4.101449275362319</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.1914893617021276</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.8212765957446808</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
